--- a/output/full_scan/batch_seq7_2026-08-18.xlsx
+++ b/output/full_scan/batch_seq7_2026-08-18.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O127"/>
+  <dimension ref="A1:O128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -527,41 +527,41 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6727</v>
+        <v>6716</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>亞泰金屬</t>
+          <t>應廣</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>978.2175220121668</v>
+        <v>1059.854130526432</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>475</v>
+        <v>137.5</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G2" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>63.5698720749952</v>
+        <v>81.07725590113165</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>16.58899323114881</v>
+        <v>31.80162312277698</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>4.940222593767301</v>
+        <v>1.585413052643219</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>14.37252069461213</v>
+        <v>6.031395398679405</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6532</v>
+        <v>6727</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>瑞耘</t>
+          <t>亞泰金屬</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>897.0891953110381</v>
+        <v>978.2175220121668</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>88.5</v>
+        <v>475</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,13 +605,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>67.03700659223446</v>
+        <v>63.5698720749952</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>28.47269205288547</v>
+        <v>16.58899323114881</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1.800595579752404</v>
+        <v>4.940222593767301</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>2.718913304115574</v>
+        <v>14.37252069461213</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6538</v>
+        <v>6532</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>倉和</t>
+          <t>瑞耘</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>823.1092488326092</v>
+        <v>897.0891953110381</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>190.5</v>
+        <v>88.5</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,13 +658,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>72.71827973316498</v>
+        <v>67.03700659223446</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>27.50505911305199</v>
+        <v>28.47269205288547</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.9109248832609228</v>
+        <v>1.800595579752404</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>4.781181657888104</v>
+        <v>2.718913304115574</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6788</v>
+        <v>6538</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>倉和</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>820.3155514455818</v>
+        <v>823.1092488326092</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>364</v>
+        <v>190.5</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>50.87231731446007</v>
+        <v>72.71827973316498</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>26.07127837296936</v>
+        <v>27.50505911305199</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.4220587872732844</v>
+        <v>0.9109248832609228</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>6.362571062012782</v>
+        <v>4.781181657888104</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6829</v>
+        <v>6788</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>千附精密</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>762.6642100736686</v>
+        <v>820.3155514455818</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>238.5</v>
+        <v>364</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,13 +764,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>63.35513030914181</v>
+        <v>50.87231731446007</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>18.21173248570942</v>
+        <v>26.07127837296936</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>2.330033822926901</v>
+        <v>0.4220587872732844</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>4</v>
@@ -782,51 +782,51 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>7.232146098786503</v>
+        <v>6.362571062012782</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6672</v>
+        <v>6829</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>騰輝電子-KY</t>
+          <t>千附精密</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>755.9578048059856</v>
+        <v>762.6642100736686</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>288</v>
+        <v>238.5</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G7" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>66.57563883831432</v>
+        <v>63.35513030914181</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>22.71234552537715</v>
+        <v>18.21173248570942</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2.061978994361071</v>
+        <v>2.330033822926901</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,48 +835,48 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>8.486683253827893</v>
+        <v>7.232146098786503</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6584</v>
+        <v>6672</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>750.1383938808347</v>
+        <v>755.9578048059856</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>596</v>
+        <v>288</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G8" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>56.64468897157575</v>
+        <v>66.57563883831432</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>26.56625369718441</v>
+        <v>22.71234552537715</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.31383938808346</v>
+        <v>2.061978994361071</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>19.56451722960839</v>
+        <v>8.486683253827893</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6651</v>
+        <v>6584</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>全宇昕</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>697.8650531668767</v>
+        <v>750.1383938808347</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>138.5</v>
+        <v>596</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>56.57372282639058</v>
+        <v>56.64468897157575</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>20.6117187201231</v>
+        <v>26.56625369718441</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.5775643690876279</v>
+        <v>1.31383938808346</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>2.916477523425453</v>
+        <v>19.56451722960839</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6761</v>
+        <v>6651</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>穩得</t>
+          <t>全宇昕</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>689.8562707000792</v>
+        <v>697.8650531668767</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>181</v>
+        <v>138.5</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>59.40930542996156</v>
+        <v>56.57372282639058</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>23.76113040318844</v>
+        <v>20.6117187201231</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.7856270700079232</v>
+        <v>0.5775643690876279</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>5.804720101278245</v>
+        <v>2.916477523425453</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6708</v>
+        <v>6761</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>天擎</t>
+          <t>穩得</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>657.4838910293181</v>
+        <v>689.8562707000792</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>40</v>
+        <v>181</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>52.17394429357427</v>
+        <v>59.40930542996156</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>10.84017898471408</v>
+        <v>23.76113040318844</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>6.688352716259238</v>
+        <v>0.7856270700079232</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,51 +1047,51 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>2.07881157690834</v>
+        <v>5.804720101278245</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6805</v>
+        <v>6708</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>天擎</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>607.2178506807833</v>
+        <v>657.4838910293181</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1960</v>
+        <v>40</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G12" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>68.08587307657841</v>
+        <v>52.17394429357427</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>31.243211695764</v>
+        <v>10.84017898471408</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.122742796479978</v>
+        <v>6.688352716259238</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>52.21422071348945</v>
+        <v>2.07881157690834</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6669</v>
+        <v>6805</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>598.1021436090413</v>
+        <v>607.2178506807833</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>6400</v>
+        <v>1960</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>62.7550826243758</v>
+        <v>68.08587307657841</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>24.58901010650466</v>
+        <v>31.243211695764</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.7181167388523597</v>
+        <v>1.122742796479978</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>49.81593979671942</v>
+        <v>52.21422071348945</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6753</v>
+        <v>6669</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>龍德造船</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>597.2181110657406</v>
+        <v>598.1021436090413</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>144.5</v>
+        <v>6400</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>53.57501900384983</v>
+        <v>62.7550826243758</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>22.45773998551475</v>
+        <v>24.58901010650466</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.9263482817320506</v>
+        <v>0.7181167388523597</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,51 +1206,51 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>1.469549685542313</v>
+        <v>49.81593979671942</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6530</v>
+        <v>6753</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>創威</t>
+          <t>龍德造船</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>591.1349795308538</v>
+        <v>597.2181110657406</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>86.7</v>
+        <v>144.5</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G15" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>57.58109644066634</v>
+        <v>53.57501900384983</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>21.52674718233856</v>
+        <v>22.45773998551475</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.231024354977601</v>
+        <v>0.9263482817320506</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>2.359565085990289</v>
+        <v>1.469549685542313</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6488</v>
+        <v>6530</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>創威</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>589.252817214333</v>
+        <v>591.1349795308538</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1020</v>
+        <v>86.7</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,49 +1294,49 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>51.67568672342249</v>
+        <v>57.58109644066634</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>16.68234969731343</v>
+        <v>21.52674718233856</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.9678060104337066</v>
+        <v>1.231024354977601</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>13.61883536260449</v>
+        <v>2.359565085990289</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, invest_trust_buy_2d, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6577</v>
+        <v>6488</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>勁豐</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>588.0722148051733</v>
+        <v>589.252817214333</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>82</v>
+        <v>1020</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,49 +1347,49 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>55.0057389789573</v>
+        <v>51.67568672342249</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>23.23767825336538</v>
+        <v>16.68234969731343</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.707041544873629</v>
+        <v>0.9678060104337066</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.1372306300135359</v>
+        <v>13.61883536260449</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, williams_r_recovery, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6640</v>
+        <v>6577</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>勁豐</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>584.1182250868895</v>
+        <v>588.0722148051733</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1070</v>
+        <v>82</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>58.29979126134359</v>
+        <v>55.0057389789573</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>20.6565284749185</v>
+        <v>23.23767825336538</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>2.111918471265116</v>
+        <v>0.707041544873629</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,48 +1418,48 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>29.97867287174777</v>
+        <v>-0.1372306300135359</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, williams_r_recovery, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6598</v>
+        <v>6640</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>ABC-KY</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>540.5868596540647</v>
+        <v>584.1182250868895</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>27.75</v>
+        <v>1070</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G19" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>49.26029995962804</v>
+        <v>58.29979126134359</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>26.07353111668851</v>
+        <v>20.6565284749185</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.3855320167120715</v>
+        <v>2.111918471265116</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,51 +1471,51 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-0.4164305724271414</v>
+        <v>29.97867287174777</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6683</v>
+        <v>6598</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>雍智科技</t>
+          <t>ABC-KY</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>538.7809120424985</v>
+        <v>540.5868596540647</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1325</v>
+        <v>27.75</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G20" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>52.36119106742599</v>
+        <v>49.26029995962804</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>21.83023887230109</v>
+        <v>26.07353111668851</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.17422289198685</v>
+        <v>0.3855320167120715</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>53.11536738626533</v>
+        <v>-0.4164305724271414</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6517</v>
+        <v>6683</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>保勝光學</t>
+          <t>雍智科技</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>538.1592391307005</v>
+        <v>538.7809120424985</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>64</v>
+        <v>1325</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>47.73405332531186</v>
+        <v>52.36119106742599</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>14.44169020704952</v>
+        <v>21.83023887230109</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.7105622431780347</v>
+        <v>1.17422289198685</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.1876290959423523</v>
+        <v>53.11536738626533</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6739</v>
+        <v>6517</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>保勝光學</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>531.1513699497066</v>
+        <v>538.1592391307005</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1025</v>
+        <v>64</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>48.68399895332854</v>
+        <v>47.73405332531186</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>9.535490894442136</v>
+        <v>14.44169020704952</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.9812401269710388</v>
+        <v>0.7105622431780347</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,51 +1630,51 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>11.46566615981516</v>
+        <v>0.1876290959423523</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6505</v>
+        <v>6739</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>529.8238331438615</v>
+        <v>531.1513699497066</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>72</v>
+        <v>1025</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G23" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>53.64717910797914</v>
+        <v>48.68399895332854</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>27.64905276913025</v>
+        <v>9.535490894442136</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.9273106219285624</v>
+        <v>0.9812401269710388</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-0.6403257216576563</v>
+        <v>11.46566615981516</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6807</v>
+        <v>6505</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>峰源-KY</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>529.6734226348597</v>
+        <v>529.8238331438615</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>37.9</v>
+        <v>72</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>68.35533081437701</v>
+        <v>53.64717910797914</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>20.8365762346695</v>
+        <v>27.64905276913025</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.166532211593869</v>
+        <v>0.9273106219285624</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,48 +1736,48 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.1660115815060945</v>
+        <v>-0.6403257216576563</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6806</v>
+        <v>6807</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>森崴能源</t>
+          <t>峰源-KY</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>528.7768356926886</v>
+        <v>529.6734226348597</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>3.51</v>
+        <v>37.9</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G25" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>31.69502755176316</v>
+        <v>68.35533081437701</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>32.59319925396388</v>
+        <v>20.8365762346695</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>2.013053626871306</v>
+        <v>1.166532211593869</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,157 +1789,157 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.411282135628904</v>
+        <v>0.1660115815060945</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6548</v>
+        <v>6806</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>長科*</t>
+          <t>森崴能源</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>527.0619851587801</v>
+        <v>528.7768356926886</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>73.2</v>
+        <v>3.51</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G26" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>49.29807905751429</v>
+        <v>31.69502755176316</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>15.10158379670315</v>
+        <v>32.59319925396388</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.3657289066708629</v>
+        <v>2.013053626871306</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.8633205457787037</v>
+        <v>0.411282135628904</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6491</v>
+        <v>6548</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>晶碩</t>
+          <t>長科*</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>519.0239748195149</v>
+        <v>527.0619851587801</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>361.5</v>
+        <v>73.2</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G27" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>53.3696330597443</v>
+        <v>49.29807905751429</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>23.7283924950891</v>
+        <v>15.10158379670315</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.4077390346161244</v>
+        <v>0.3657289066708629</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.08844748973929301</v>
+        <v>0.8633205457787037</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6642</v>
+        <v>6491</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>富致</t>
+          <t>晶碩</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>508.1578770420836</v>
+        <v>519.0239748195149</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>83.7</v>
+        <v>361.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G28" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>57.76329083912749</v>
+        <v>53.3696330597443</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>21.06292897531807</v>
+        <v>23.7283924950891</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.3844627324066902</v>
+        <v>0.4077390346161244</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,51 +1948,51 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>1.276940801538027</v>
+        <v>-0.08844748973929301</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6658</v>
+        <v>6642</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>聯策</t>
+          <t>富致</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>498.1034474803878</v>
+        <v>508.1578770420836</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>161.5</v>
+        <v>83.7</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G29" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>49.19612324325536</v>
+        <v>57.76329083912749</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>16.70355688255189</v>
+        <v>21.06292897531807</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.7051691533917318</v>
+        <v>0.3844627324066902</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>2.977531313181305</v>
+        <v>1.276940801538027</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6691</v>
+        <v>6658</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>聯策</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>496.2035836268618</v>
+        <v>498.1034474803878</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>713</v>
+        <v>161.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>50.91147838675373</v>
+        <v>49.19612324325536</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>13.19250516122956</v>
+        <v>16.70355688255189</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.731109899963355</v>
+        <v>0.7051691533917318</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,51 +2054,51 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>4.037638954283199</v>
+        <v>2.977531313181305</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6570</v>
+        <v>6691</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>維田</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>491.3793325008196</v>
+        <v>496.2035836268618</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>55.5</v>
+        <v>713</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G31" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>55.77834445673251</v>
+        <v>50.91147838675373</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>18.01109412822886</v>
+        <v>13.19250516122956</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.4036975835794778</v>
+        <v>1.731109899963355</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,51 +2107,51 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.3124800444071665</v>
+        <v>4.037638954283199</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6589</v>
+        <v>6570</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>台康生技</t>
+          <t>維田</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>487.8568521541223</v>
+        <v>491.3793325008196</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>48.7</v>
+        <v>55.5</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G32" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>51.48378527572751</v>
+        <v>55.77834445673251</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>26.48896579900689</v>
+        <v>18.01109412822886</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.4632655639874992</v>
+        <v>0.4036975835794778</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.1518175383125063</v>
+        <v>0.3124800444071665</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6533</v>
+        <v>6589</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>台康生技</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>484.2297358601859</v>
+        <v>487.8568521541223</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>245</v>
+        <v>48.7</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>58.58295249577996</v>
+        <v>51.48378527572751</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>14.06646134005417</v>
+        <v>26.48896579900689</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.5252819464385703</v>
+        <v>0.4632655639874992</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,51 +2213,51 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>1.055985808595196</v>
+        <v>0.1518175383125063</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6664</v>
+        <v>6533</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>群翊</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>473.2799852108602</v>
+        <v>484.2297358601859</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>342</v>
+        <v>245</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G34" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>45.48491487057336</v>
+        <v>58.58295249577996</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>21.32829645922326</v>
+        <v>14.06646134005417</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.5545598757570823</v>
+        <v>0.5252819464385703</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,51 +2266,51 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>2.61424521928218</v>
+        <v>1.055985808595196</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6715</v>
+        <v>6664</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>嘉基</t>
+          <t>群翊</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>471.966568691121</v>
+        <v>473.2799852108602</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>419</v>
+        <v>342</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G35" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>57.02678824080632</v>
+        <v>45.48491487057336</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>12.58974766869183</v>
+        <v>21.32829645922326</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.518708023046029</v>
+        <v>0.5545598757570823</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>10.06355425352639</v>
+        <v>2.61424521928218</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6770</v>
+        <v>6715</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>嘉基</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>471.2044409457163</v>
+        <v>471.966568691121</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>69.7</v>
+        <v>419</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>52.26030739340654</v>
+        <v>57.02678824080632</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>16.40036546415717</v>
+        <v>12.58974766869183</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.9874502695889744</v>
+        <v>1.518708023046029</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>1.74574889865442</v>
+        <v>10.06355425352639</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6666</v>
+        <v>6770</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>羅麗芬-KY</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>465.0454521138218</v>
+        <v>471.2044409457163</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>43.7</v>
+        <v>69.7</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>52.45924520239569</v>
+        <v>52.26030739340654</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>26.12385095066193</v>
+        <v>16.40036546415717</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.4994090497916818</v>
+        <v>0.9874502695889744</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.0286589649682743</v>
+        <v>1.74574889865442</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6606</v>
+        <v>6666</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>建德工業</t>
+          <t>羅麗芬-KY</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>449.4695957339949</v>
+        <v>465.0454521138218</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>26.35</v>
+        <v>43.7</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>52.49504422238352</v>
+        <v>52.45924520239569</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>15.43688072735711</v>
+        <v>26.12385095066193</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.133208535189213</v>
+        <v>0.4994090497916818</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.0427901365298716</v>
+        <v>-0.0286589649682743</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6585</v>
+        <v>6606</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>鼎基</t>
+          <t>建德工業</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>439.0146711778009</v>
+        <v>449.4695957339949</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>116.5</v>
+        <v>26.35</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>46.45233597929115</v>
+        <v>52.49504422238352</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>14.90854931555071</v>
+        <v>15.43688072735711</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.7777991438968345</v>
+        <v>1.133208535189213</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.3498677915419088</v>
+        <v>0.0427901365298716</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6605</v>
+        <v>6585</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>帝寶</t>
+          <t>鼎基</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>438.9479735876079</v>
+        <v>439.0146711778009</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>138</v>
+        <v>116.5</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>54.66730156913272</v>
+        <v>46.45233597929115</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>12.40384632523452</v>
+        <v>14.90854931555071</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.4554383787217764</v>
+        <v>0.7777991438968345</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,51 +2584,51 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.4936863476698914</v>
+        <v>0.3498677915419088</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6498</v>
+        <v>6605</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>久禾光</t>
+          <t>帝寶</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>437.9923922753663</v>
+        <v>438.9479735876079</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>77.90000000000001</v>
+        <v>138</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G41" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>47.85885533640482</v>
+        <v>54.66730156913272</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>33.37532114361925</v>
+        <v>12.40384632523452</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.120095138066897</v>
+        <v>0.4554383787217764</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,51 +2637,51 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>1.094395932396338</v>
+        <v>0.4936863476698914</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6525</v>
+        <v>6498</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>捷敏-KY</t>
+          <t>久禾光</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>436.2851804978626</v>
+        <v>437.9923922753663</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>148</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G42" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>51.86179045895824</v>
+        <v>47.85885533640482</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>16.27368796972114</v>
+        <v>33.37532114361925</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>2.019693131470539</v>
+        <v>1.120095138066897</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,48 +2690,48 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>2.0055073949218</v>
+        <v>1.094395932396338</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6597</v>
+        <v>6525</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>立誠</t>
+          <t>捷敏-KY</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>435.5916168365934</v>
+        <v>436.2851804978626</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>68.7</v>
+        <v>148</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G43" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>52.23029727889998</v>
+        <v>51.86179045895824</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>9.544294426541136</v>
+        <v>16.27368796972114</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.014670371673684</v>
+        <v>2.019693131470539</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.4176282538037466</v>
+        <v>2.0055073949218</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6811</v>
+        <v>6597</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>宏碁資訊</t>
+          <t>立誠</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>434.0942626642558</v>
+        <v>435.5916168365934</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>227</v>
+        <v>68.7</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>48.57998121112924</v>
+        <v>52.23029727889998</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>18.77522299503554</v>
+        <v>9.544294426541136</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.7529478002091209</v>
+        <v>1.014670371673684</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,48 +2796,48 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.1776008106642961</v>
+        <v>-0.4176282538037466</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
+          <t>breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6782</v>
+        <v>6811</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>視陽</t>
+          <t>宏碁資訊</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>433.5356350320883</v>
+        <v>434.0942626642558</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>198.5</v>
+        <v>227</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G45" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>49.70304676398594</v>
+        <v>48.57998121112924</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>22.17268140725972</v>
+        <v>18.77522299503554</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.2580971502959554</v>
+        <v>0.7529478002091209</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,48 +2849,48 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.5055419189981341</v>
+        <v>-0.1776008106642961</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6546</v>
+        <v>6782</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>正基</t>
+          <t>視陽</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>433.2048367975365</v>
+        <v>433.5356350320883</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>62.9</v>
+        <v>198.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G46" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>50.93737053430893</v>
+        <v>49.70304676398594</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>27.39839213559473</v>
+        <v>22.17268140725972</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.5554445762594884</v>
+        <v>0.2580971502959554</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,48 +2902,48 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>1.235722059432203</v>
+        <v>0.5055419189981341</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6526</v>
+        <v>6546</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>正基</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>425.0869579715616</v>
+        <v>433.2048367975365</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>579</v>
+        <v>62.9</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G47" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>44.10907192170213</v>
+        <v>50.93737053430893</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>13.99367746510011</v>
+        <v>27.39839213559473</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.8289920456563001</v>
+        <v>0.5554445762594884</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>4.043798205764016</v>
+        <v>1.235722059432203</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6789</v>
+        <v>6526</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>423.9855641848593</v>
+        <v>425.0869579715616</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>433</v>
+        <v>579</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>43.83751127876515</v>
+        <v>44.10907192170213</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>22.00747417804584</v>
+        <v>13.99367746510011</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.6566941517807731</v>
+        <v>0.8289920456563001</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>2.936784542518751</v>
+        <v>4.043798205764016</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6834</v>
+        <v>6789</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>天二科技</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>421.2873818692345</v>
+        <v>423.9855641848593</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>95.2</v>
+        <v>433</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>48.23020515971167</v>
+        <v>43.83751127876515</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>17.32420621727479</v>
+        <v>22.00747417804584</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.5822549700702224</v>
+        <v>0.6566941517807731</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,51 +3061,51 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>1.247447228800568</v>
+        <v>2.936784542518751</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6720</v>
+        <v>6834</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>久昌</t>
+          <t>天二科技</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>412.2539513123938</v>
+        <v>421.2873818692345</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>138</v>
+        <v>95.2</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G50" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>49.40042173515035</v>
+        <v>48.23020515971167</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>22.34041247063493</v>
+        <v>17.32420621727479</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.1433976602553811</v>
+        <v>0.5822549700702224</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,51 +3114,51 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.6254767102196521</v>
+        <v>1.247447228800568</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6757</v>
+        <v>6720</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>台灣虎航-創</t>
+          <t>久昌</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>410.6053143389608</v>
+        <v>412.2539513123938</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>56.6</v>
+        <v>138</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G51" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>50.69296122181783</v>
+        <v>49.40042173515035</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>11.06909834204181</v>
+        <v>22.34041247063493</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.9422838882096988</v>
+        <v>0.1433976602553811</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,51 +3167,51 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.0630136999912583</v>
+        <v>0.6254767102196521</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6485</v>
+        <v>6757</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>點序</t>
+          <t>台灣虎航-創</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>402.3358115936652</v>
+        <v>410.6053143389608</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>61.7</v>
+        <v>56.6</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G52" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>41.66179653030755</v>
+        <v>50.69296122181783</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>24.75513315509651</v>
+        <v>11.06909834204181</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.6199392787573492</v>
+        <v>0.9422838882096988</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,51 +3220,51 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>1.283739550966299</v>
+        <v>0.0630136999912583</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6534</v>
+        <v>6485</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>正瀚-創</t>
+          <t>點序</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>401.0627503704382</v>
+        <v>402.3358115936652</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>91.09999999999999</v>
+        <v>61.7</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G53" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>39.72350813093074</v>
+        <v>41.66179653030755</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>22.33358936763074</v>
+        <v>24.75513315509651</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.4055307196265379</v>
+        <v>0.6199392787573492</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,48 +3273,48 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.3400460462629576</v>
+        <v>1.283739550966299</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6560</v>
+        <v>6534</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>欣普羅</t>
+          <t>正瀚-創</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>399.0216580039007</v>
+        <v>401.0627503704382</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>31</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G54" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>33.44539449023512</v>
+        <v>39.72350813093074</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>21.60883216218146</v>
+        <v>22.33358936763074</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>2.88134419477703</v>
+        <v>0.4055307196265379</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,48 +3326,48 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.1347885311238155</v>
+        <v>-0.3400460462629576</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6796</v>
+        <v>6560</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>晉弘</t>
+          <t>欣普羅</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>397.2026552092022</v>
+        <v>399.0216580039007</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>59.6</v>
+        <v>31</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G55" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>54.58728161578219</v>
+        <v>33.44539449023512</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>21.43017156396796</v>
+        <v>21.60883216218146</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.9532372140669784</v>
+        <v>2.88134419477703</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.3779421665291206</v>
+        <v>0.1347885311238155</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6550</v>
+        <v>6796</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>北極星藥業-KY</t>
+          <t>晉弘</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>391.4255211727148</v>
+        <v>397.2026552092022</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>10.3</v>
+        <v>59.6</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>28.59414598185347</v>
+        <v>54.58728161578219</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>27.57978175027729</v>
+        <v>21.43017156396796</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>2.262511061873811</v>
+        <v>0.9532372140669784</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,48 +3432,48 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.0076171892948331</v>
+        <v>0.3779421665291206</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6741</v>
+        <v>6550</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>91APP*-KY</t>
+          <t>北極星藥業-KY</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>390.0675977974635</v>
+        <v>391.4255211727148</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>54.7</v>
+        <v>10.3</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G57" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>39.13708382185594</v>
+        <v>28.59414598185347</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>26.80241178470726</v>
+        <v>27.57978175027729</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.4967842693418883</v>
+        <v>2.262511061873811</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.1595054981134676</v>
+        <v>0.0076171892948331</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6643</v>
+        <v>6741</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>91APP*-KY</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>388.0155637983354</v>
+        <v>390.0675977974635</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>432</v>
+        <v>54.7</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>48.1922968401641</v>
+        <v>39.13708382185594</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>18.83772712339038</v>
+        <v>26.80241178470726</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.4809577084878456</v>
+        <v>0.4967842693418883</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>5.839943245109332</v>
+        <v>0.1595054981134676</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6510</v>
+        <v>6643</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>372.2062758676193</v>
+        <v>388.0155637983354</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>2880</v>
+        <v>432</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>52.52057010725671</v>
+        <v>48.1922968401641</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>19.9149645363553</v>
+        <v>18.83772712339038</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.350351027030906</v>
+        <v>0.4809577084878456</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,48 +3591,48 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>56.20301521164848</v>
+        <v>5.839943245109332</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6781</v>
+        <v>6510</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>AES-KY</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>371.5747866294256</v>
+        <v>372.2062758676193</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>1060</v>
+        <v>2880</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G60" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>48.52454764976507</v>
+        <v>52.52057010725671</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>18.80871059782591</v>
+        <v>19.9149645363553</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.6342768743349655</v>
+        <v>1.350351027030906</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,7 +3644,7 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>10.8433362184924</v>
+        <v>56.20301521164848</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
@@ -3654,38 +3654,38 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6692</v>
+        <v>6781</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>進能服</t>
+          <t>AES-KY</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>370.4950529580905</v>
+        <v>371.5747866294256</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>24.5</v>
+        <v>1060</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G61" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>52.91999743686578</v>
+        <v>48.52454764976507</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>9.921289832214841</v>
+        <v>18.80871059782591</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.6817538582773298</v>
+        <v>0.6342768743349655</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,48 +3697,48 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.4802135393455665</v>
+        <v>10.8433362184924</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6706</v>
+        <v>6692</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>惠特</t>
+          <t>進能服</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>365.8875727398594</v>
+        <v>370.4950529580905</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>118.5</v>
+        <v>24.5</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G62" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>49.28540682436581</v>
+        <v>52.91999743686578</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>18.9073810334883</v>
+        <v>9.921289832214841</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.5086092894063508</v>
+        <v>0.6817538582773298</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>3.502214624385167</v>
+        <v>0.4802135393455665</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6756</v>
+        <v>6706</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>威鋒電子</t>
+          <t>惠特</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>365.0802607921493</v>
+        <v>365.8875727398594</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>97.2</v>
+        <v>118.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>49.7370677756207</v>
+        <v>49.28540682436581</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>12.69159609288674</v>
+        <v>18.9073810334883</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.5734206520973276</v>
+        <v>0.5086092894063508</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,51 +3803,51 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.3876242777334066</v>
+        <v>3.502214624385167</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6821</v>
+        <v>6756</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>聯寶</t>
+          <t>威鋒電子</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>363.9292186199035</v>
+        <v>365.0802607921493</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>41.9</v>
+        <v>97.2</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G64" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>40.46350368865797</v>
+        <v>49.7370677756207</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>26.19171946495782</v>
+        <v>12.69159609288674</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.3400187949770739</v>
+        <v>0.5734206520973276</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.8619881206152522</v>
+        <v>0.3876242777334066</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6693</v>
+        <v>6821</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>廣閎科</t>
+          <t>聯寶</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>360.807203870467</v>
+        <v>363.9292186199035</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>181</v>
+        <v>41.9</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,102 +3891,102 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>49.0969457571095</v>
+        <v>40.46350368865797</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>19.86233693603153</v>
+        <v>26.19171946495782</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.8153952659212987</v>
+        <v>0.3400187949770739</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M65" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>3.275563580278589</v>
+        <v>0.8619881206152522</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6831</v>
+        <v>6693</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>邁科</t>
+          <t>廣閎科</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>360.0503610010305</v>
+        <v>360.807203870467</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>655</v>
+        <v>181</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G66" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>50.05661233633035</v>
+        <v>49.0969457571095</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>18.97031778408633</v>
+        <v>19.86233693603153</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.7544899660542624</v>
+        <v>0.8153952659212987</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>15.01326116283337</v>
+        <v>3.275563580278589</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6645</v>
+        <v>6831</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>金萬林-創</t>
+          <t>邁科</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>357.4341742609499</v>
+        <v>360.0503610010305</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>12.85</v>
+        <v>655</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>37.73465830281981</v>
+        <v>50.05661233633035</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>25.27316624559637</v>
+        <v>18.97031778408633</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.6617409019121769</v>
+        <v>0.7544899660542624</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,51 +4015,51 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.0126134978387686</v>
+        <v>15.01326116283337</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6568</v>
+        <v>6645</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>宏觀</t>
+          <t>金萬林-創</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>356.9807792708143</v>
+        <v>357.4341742609499</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>133</v>
+        <v>12.85</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G68" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>38.8641231161986</v>
+        <v>37.73465830281981</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>47.40697939225761</v>
+        <v>25.27316624559637</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.2917762811968581</v>
+        <v>0.6617409019121769</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,51 +4068,51 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>1.578297664358787</v>
+        <v>0.0126134978387686</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6719</v>
+        <v>6568</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>宏觀</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>355.6569592517104</v>
+        <v>356.9807792708143</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>194.5</v>
+        <v>133</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G69" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>36.56043266459635</v>
+        <v>38.8641231161986</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>20.65035684546872</v>
+        <v>47.40697939225761</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.546323223231845</v>
+        <v>0.2917762811968581</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.1804724273632665</v>
+        <v>1.578297664358787</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6771</v>
+        <v>6719</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>平和環保-創</t>
+          <t>力智</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>355.2680306569134</v>
+        <v>355.6569592517104</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>41.5</v>
+        <v>194.5</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>70.20761190801204</v>
+        <v>36.56043266459635</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>29.7696771226333</v>
+        <v>20.65035684546872</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.9890068770496842</v>
+        <v>0.546323223231845</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,51 +4174,51 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.4914248431324214</v>
+        <v>0.1804724273632665</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6494</v>
+        <v>6771</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>九齊</t>
+          <t>平和環保-創</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>352.4790923106098</v>
+        <v>355.2680306569134</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>54.7</v>
+        <v>41.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G71" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>52.45552858084518</v>
+        <v>70.20761190801204</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>19.73025273005377</v>
+        <v>29.7696771226333</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.5331066315381002</v>
+        <v>0.9890068770496842</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,51 +4227,51 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>1.038913578996074</v>
+        <v>0.4914248431324214</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6531</v>
+        <v>6494</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>九齊</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>346.3044967237201</v>
+        <v>352.4790923106098</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>863</v>
+        <v>54.7</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G72" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>50.21855187050981</v>
+        <v>52.45552858084518</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>12.47046964547794</v>
+        <v>19.73025273005377</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>2.478233796991175</v>
+        <v>0.5331066315381002</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>14.04014095460891</v>
+        <v>1.038913578996074</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6670</v>
+        <v>6531</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>337.8714784880222</v>
+        <v>346.3044967237201</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>261.5</v>
+        <v>863</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>47.62213038544639</v>
+        <v>50.21855187050981</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>11.13045689893268</v>
+        <v>12.47046964547794</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.2706360876274331</v>
+        <v>2.478233796991175</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.0776770666695967</v>
+        <v>14.04014095460891</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6743</v>
+        <v>6670</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>安普新</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>337.2959712137071</v>
+        <v>337.8714784880222</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>24.95</v>
+        <v>261.5</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>34.41836609595296</v>
+        <v>47.62213038544639</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>25.37586762183983</v>
+        <v>11.13045689893268</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.6684017857142858</v>
+        <v>0.2706360876274331</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.2274983835627955</v>
+        <v>-0.0776770666695967</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6698</v>
+        <v>6743</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>旭暉應材</t>
+          <t>安普新</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>323.6813163186617</v>
+        <v>337.2959712137071</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>30.95</v>
+        <v>24.95</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>35.93956219688255</v>
+        <v>34.41836609595296</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>25.60462649721305</v>
+        <v>25.37586762183983</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.4738787663448298</v>
+        <v>0.6684017857142858</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.0524980842295559</v>
+        <v>-0.2274983835627955</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6674</v>
+        <v>6698</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>鋐寶科技</t>
+          <t>旭暉應材</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>311.7391120464316</v>
+        <v>323.6813163186617</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>14.75</v>
+        <v>30.95</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>31.2406709616668</v>
+        <v>35.93956219688255</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>28.69671255425146</v>
+        <v>25.60462649721305</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.180793499912805</v>
+        <v>0.4738787663448298</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,51 +4492,51 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.0194336266823078</v>
+        <v>0.0524980842295559</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6763</v>
+        <v>6674</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>綠界科技</t>
+          <t>鋐寶科技</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>309.4615411492487</v>
+        <v>311.7391120464316</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>41.85</v>
+        <v>14.75</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G77" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>41.86926924414122</v>
+        <v>31.2406709616668</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>23.96705376450203</v>
+        <v>28.69671255425146</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.4544152120055755</v>
+        <v>1.180793499912805</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,51 +4545,51 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.1835962010008772</v>
+        <v>-0.0194336266823078</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6830</v>
+        <v>6763</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>汎銓</t>
+          <t>綠界科技</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>304.3927684653413</v>
+        <v>309.4615411492487</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>431.5</v>
+        <v>41.85</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G78" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>53.25359770797798</v>
+        <v>41.86926924414122</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>18.0205984668349</v>
+        <v>23.96705376450203</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.8661362598004173</v>
+        <v>0.4544152120055755</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>11.04948135952842</v>
+        <v>0.1835962010008772</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6689</v>
+        <v>6830</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>伊雲谷</t>
+          <t>汎銓</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>304.2789096903779</v>
+        <v>304.3927684653413</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>60.2</v>
+        <v>431.5</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>44.61252393352763</v>
+        <v>53.25359770797798</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>18.44068456033326</v>
+        <v>18.0205984668349</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.5031879142398444</v>
+        <v>0.8661362598004173</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.29367120846106</v>
+        <v>11.04948135952842</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6799</v>
+        <v>6689</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>來頡</t>
+          <t>伊雲谷</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>302.3793359458062</v>
+        <v>304.2789096903779</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>78.8</v>
+        <v>60.2</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>40.49889439745973</v>
+        <v>44.61252393352763</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>17.35524762693432</v>
+        <v>18.44068456033326</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.698866805699858</v>
+        <v>0.5031879142398444</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,7 +4704,7 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.4437272865706583</v>
+        <v>0.29367120846106</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
@@ -4714,21 +4714,21 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6671</v>
+        <v>6799</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>三能-KY</t>
+          <t>來頡</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>300.937368244817</v>
+        <v>302.3793359458062</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>22.3</v>
+        <v>78.8</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>33.10418409650175</v>
+        <v>40.49889439745973</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>31.43893658000749</v>
+        <v>17.35524762693432</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.3165665946590735</v>
+        <v>0.698866805699858</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.0375920612263571</v>
+        <v>0.4437272865706583</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6835</v>
+        <v>6671</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>圓裕</t>
+          <t>三能-KY</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>296.4328646139074</v>
+        <v>300.937368244817</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>31</v>
+        <v>22.3</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>40.5064568513497</v>
+        <v>33.10418409650175</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>29.58958592185187</v>
+        <v>31.43893658000749</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.6483991267333136</v>
+        <v>0.3165665946590735</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.2244002559897302</v>
+        <v>0.0375920612263571</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6515</v>
+        <v>6835</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>圓裕</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>294.3152884517982</v>
+        <v>296.4328646139074</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>6315</v>
+        <v>31</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>42.16921747180085</v>
+        <v>40.5064568513497</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>14.81112876282743</v>
+        <v>29.58958592185187</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.9589039407500896</v>
+        <v>0.6483991267333136</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>94.5801261831934</v>
+        <v>0.2244002559897302</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6742</v>
+        <v>6515</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>澤米</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>293.7672160202291</v>
+        <v>294.3152884517982</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>43.75</v>
+        <v>6315</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>41.62561275848313</v>
+        <v>42.16921747180085</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>19.69499818978296</v>
+        <v>14.81112876282743</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.814715610096397</v>
+        <v>0.9589039407500896</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,51 +4916,51 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.6499544354781372</v>
+        <v>94.5801261831934</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6679</v>
+        <v>6742</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>鈺太</t>
+          <t>澤米</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>292.6040189693819</v>
+        <v>293.7672160202291</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>206.5</v>
+        <v>43.75</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G85" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>40.12627502350426</v>
+        <v>41.62561275848313</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>27.14724586022948</v>
+        <v>19.69499818978296</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.3649819857373551</v>
+        <v>0.814715610096397</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>1.638919906077309</v>
+        <v>0.6499544354781372</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6690</v>
+        <v>6679</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>鈺太</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>285.6920121674235</v>
+        <v>292.6040189693819</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>164.5</v>
+        <v>206.5</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>50.33564433594888</v>
+        <v>40.12627502350426</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>15.63968704490507</v>
+        <v>27.14724586022948</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.6977882091307989</v>
+        <v>0.3649819857373551</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.6749589222113586</v>
+        <v>1.638919906077309</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6680</v>
+        <v>6690</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>鑫創電子</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>283.6790909249526</v>
+        <v>285.6920121674235</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>52.9</v>
+        <v>164.5</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>51.58083851650501</v>
+        <v>50.33564433594888</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>8.69698064321353</v>
+        <v>15.63968704490507</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.1485604036806174</v>
+        <v>0.6977882091307989</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.3194009383931016</v>
+        <v>0.6749589222113586</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6654</v>
+        <v>6680</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>天正國際</t>
+          <t>鑫創電子</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>282.8520535993841</v>
+        <v>283.6790909249526</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>175.5</v>
+        <v>52.9</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>51.40227082732097</v>
+        <v>51.58083851650501</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>16.59206528985673</v>
+        <v>8.69698064321353</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.0212579769876628</v>
+        <v>0.1485604036806174</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>1.417617272781436</v>
+        <v>-0.3194009383931016</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6512</v>
+        <v>6654</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>啟發電</t>
+          <t>天正國際</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>282.0283160334661</v>
+        <v>282.8520535993841</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>20.4</v>
+        <v>175.5</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>53.04556951556711</v>
+        <v>51.40227082732097</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>8.693541766223955</v>
+        <v>16.59206528985673</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.131250675243295</v>
+        <v>0.0212579769876628</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,48 +5181,48 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.7124037033777524</v>
+        <v>1.417617272781436</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6792</v>
+        <v>6512</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>詠業</t>
+          <t>啟發電</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>278.2700414576859</v>
+        <v>282.0283160334661</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>58.5</v>
+        <v>20.4</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G90" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>53.74245043107028</v>
+        <v>53.04556951556711</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>14.50468683328638</v>
+        <v>8.693541766223955</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.2852405889674283</v>
+        <v>1.131250675243295</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.8164149152501899</v>
+        <v>0.7124037033777524</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6591</v>
+        <v>6792</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>動力-KY</t>
+          <t>詠業</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>272.4586699864964</v>
+        <v>278.2700414576859</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>43.35</v>
+        <v>58.5</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>38.4782263975959</v>
+        <v>53.74245043107028</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>36.33714373841608</v>
+        <v>14.50468683328638</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.8035926774162642</v>
+        <v>0.2852405889674283</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,48 +5287,48 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.3352884441810544</v>
+        <v>0.8164149152501899</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6613</v>
+        <v>6591</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>朋億*</t>
+          <t>動力-KY</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>271.525184567371</v>
+        <v>272.4586699864964</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>262.5</v>
+        <v>43.35</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G92" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>39.16029914231961</v>
+        <v>38.4782263975959</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>13.56229115738236</v>
+        <v>36.33714373841608</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.7054725774045952</v>
+        <v>0.8035926774162642</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,48 +5340,48 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-1.261659082192839</v>
+        <v>0.3352884441810544</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6592</v>
+        <v>6613</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>和潤企業</t>
+          <t>朋億*</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>269.3772487077123</v>
+        <v>271.525184567371</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>60.6</v>
+        <v>262.5</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G93" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>47.14610754638046</v>
+        <v>39.16029914231961</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>9.8777504402087</v>
+        <v>13.56229115738236</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.4121690889350388</v>
+        <v>0.7054725774045952</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.1236914132576325</v>
+        <v>-1.261659082192839</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6579</v>
+        <v>6592</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>研揚</t>
+          <t>和潤企業</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>266.5682704525514</v>
+        <v>269.3772487077123</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>151</v>
+        <v>60.6</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>42.02275474208588</v>
+        <v>47.14610754638046</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>11.43789820119551</v>
+        <v>9.8777504402087</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.3875966166115697</v>
+        <v>0.4121690889350388</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,51 +5446,51 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-1.871397084529168</v>
+        <v>0.1236914132576325</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6684</v>
+        <v>6579</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>安格</t>
+          <t>研揚</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>263.1043338610228</v>
+        <v>266.5682704525514</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>47.15</v>
+        <v>151</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G95" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>42.06071645555128</v>
+        <v>42.02275474208588</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>13.93354043778156</v>
+        <v>11.43789820119551</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.9475436727161944</v>
+        <v>0.3875966166115697</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,51 +5499,51 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.2410877490942535</v>
+        <v>-1.871397084529168</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6768</v>
+        <v>6684</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>志強-KY</t>
+          <t>安格</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>262.5196384388065</v>
+        <v>263.1043338610228</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>63.7</v>
+        <v>47.15</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G96" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>30.36472301924867</v>
+        <v>42.06071645555128</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>34.65463988055701</v>
+        <v>13.93354043778156</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.308576130083944</v>
+        <v>0.9475436727161944</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.1582240899261302</v>
+        <v>0.2410877490942535</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6558</v>
+        <v>6768</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>興能高</t>
+          <t>志強-KY</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>255.1805496782992</v>
+        <v>262.5196384388065</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>25</v>
+        <v>63.7</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>40.18321789224704</v>
+        <v>30.36472301924867</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>27.9379559844342</v>
+        <v>34.65463988055701</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.5699782288672939</v>
+        <v>1.308576130083944</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.1665022985256705</v>
+        <v>0.1582240899261302</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6504</v>
+        <v>6558</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>南六</t>
+          <t>興能高</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>254.867964140349</v>
+        <v>255.1805496782992</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>37.1</v>
+        <v>25</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>41.51249211558046</v>
+        <v>40.18321789224704</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>25.44179184700887</v>
+        <v>27.9379559844342</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.4451912715517241</v>
+        <v>0.5699782288672939</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,48 +5658,48 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.283318008560651</v>
+        <v>0.1665022985256705</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6624</v>
+        <v>6504</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>萬年清</t>
+          <t>南六</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>252.0677055585816</v>
+        <v>254.867964140349</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>41.8</v>
+        <v>37.1</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G99" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>53.52984717876027</v>
+        <v>41.51249211558046</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>9.409959787475618</v>
+        <v>25.44179184700887</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.0542821105327827</v>
+        <v>0.4451912715517241</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>2.224992149714162</v>
+        <v>-0.283318008560651</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6735</v>
+        <v>6624</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>美達科技</t>
+          <t>萬年清</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>251.88685346335</v>
+        <v>252.0677055585816</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>64.3</v>
+        <v>41.8</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>41.18683986456349</v>
+        <v>53.52984717876027</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>22.63755556050528</v>
+        <v>9.409959787475618</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.7925894699047397</v>
+        <v>0.0542821105327827</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.97611376011508</v>
+        <v>2.224992149714162</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6588</v>
+        <v>6735</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>東典光電</t>
+          <t>美達科技</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>249.603732678166</v>
+        <v>251.88685346335</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>90.90000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>51.26906105019144</v>
+        <v>41.18683986456349</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>18.02369378204456</v>
+        <v>22.63755556050528</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.2487070199791353</v>
+        <v>0.7925894699047397</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>1</v>
@@ -5817,51 +5817,51 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.9958479231645048</v>
+        <v>0.97611376011508</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6655</v>
+        <v>6588</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>科定</t>
+          <t>東典光電</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>249.1349560887997</v>
+        <v>249.603732678166</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>115</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G102" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>44.61260609139691</v>
+        <v>51.26906105019144</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>6.733267387462194</v>
+        <v>18.02369378204456</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.8163198667765977</v>
+        <v>0.2487070199791353</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,51 +5870,51 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.2642859928575199</v>
+        <v>0.9958479231645048</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6667</v>
+        <v>6655</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>信紘科</t>
+          <t>科定</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>242.1910747735316</v>
+        <v>249.1349560887997</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>226</v>
+        <v>115</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G103" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>41.92496350564397</v>
+        <v>44.61260609139691</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>27.04492844849068</v>
+        <v>6.733267387462194</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.4867519555620806</v>
+        <v>0.8163198667765977</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,51 +5923,51 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.7600665270942306</v>
+        <v>-0.2642859928575199</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6722</v>
+        <v>6667</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>輝創</t>
+          <t>信紘科</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>238.4785935607772</v>
+        <v>242.1910747735316</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>32.25</v>
+        <v>226</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G104" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>34.11413448572036</v>
+        <v>41.92496350564397</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>43.65275132849257</v>
+        <v>27.04492844849068</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.3482706353646549</v>
+        <v>0.4867519555620806</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,48 +5976,48 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.0332395634628073</v>
+        <v>0.7600665270942306</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6803</v>
+        <v>6722</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>崑鼎</t>
+          <t>輝創</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>235.7618854492669</v>
+        <v>238.4785935607772</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>269</v>
+        <v>32.25</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G105" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>39.45083508067049</v>
+        <v>34.11413448572036</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>33.22005520793678</v>
+        <v>43.65275132849257</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.3772711150501724</v>
+        <v>0.3482706353646549</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,7 +6029,7 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.3568697634770488</v>
+        <v>0.0332395634628073</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6039,38 +6039,38 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6541</v>
+        <v>6803</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>泰福-KY</t>
+          <t>崑鼎</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>235.7131688962248</v>
+        <v>235.7618854492669</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>35.5</v>
+        <v>269</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G106" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>34.35969722124389</v>
+        <v>39.45083508067049</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>9.88121370210686</v>
+        <v>33.22005520793678</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>2.130388229171822</v>
+        <v>0.3772711150501724</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,28 +6082,28 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.1211809776996939</v>
+        <v>0.3568697634770488</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6668</v>
+        <v>6541</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>中揚光</t>
+          <t>泰福-KY</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>234.5586058059913</v>
+        <v>235.7131688962248</v>
       </c>
       <c r="E107" s="2" t="n">
         <v>35.5</v>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>47.8214876513593</v>
+        <v>34.35969722124389</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>17.374730809404</v>
+        <v>9.88121370210686</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.3896333470361491</v>
+        <v>2.130388229171822</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,51 +6135,51 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.2386001101920892</v>
+        <v>-0.1211809776996939</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6486</v>
+        <v>6668</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>互動</t>
+          <t>中揚光</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>233.361005246468</v>
+        <v>234.5586058059913</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>73.8</v>
+        <v>35.5</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G108" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>33.77331603932616</v>
+        <v>47.8214876513593</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>22.58933591440569</v>
+        <v>17.374730809404</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.959203388038275</v>
+        <v>0.3896333470361491</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,51 +6188,51 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.1223964010978786</v>
+        <v>0.2386001101920892</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6657</v>
+        <v>6486</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>華安</t>
+          <t>互動</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>233.2328793766794</v>
+        <v>233.361005246468</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>29.7</v>
+        <v>73.8</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G109" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>36.10641304037623</v>
+        <v>33.77331603932616</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>28.30183145116655</v>
+        <v>22.58933591440569</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.075311076696653</v>
+        <v>0.959203388038275</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,7 +6241,7 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.076357766376039</v>
+        <v>0.1223964010978786</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
@@ -6251,21 +6251,21 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6625</v>
+        <v>6657</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>必應</t>
+          <t>華安</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>232.2146964201615</v>
+        <v>233.2328793766794</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>76.8</v>
+        <v>29.7</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>50.18060786948606</v>
+        <v>36.10641304037623</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>12.26676780066278</v>
+        <v>28.30183145116655</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.5817885924146694</v>
+        <v>1.075311076696653</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.1495839250601227</v>
+        <v>0.076357766376039</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6695</v>
+        <v>6625</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>芯鼎</t>
+          <t>必應</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>229.0166592961561</v>
+        <v>232.2146964201615</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>48.3</v>
+        <v>76.8</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>41.13161433526319</v>
+        <v>50.18060786948606</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>14.34201936916479</v>
+        <v>12.26676780066278</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.5488437355316024</v>
+        <v>0.5817885924146694</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.1404900519776275</v>
+        <v>0.1495839250601227</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6776</v>
+        <v>6695</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>芯鼎</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>200.4248547505902</v>
+        <v>229.0166592961561</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>53.4</v>
+        <v>48.3</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>44.1694646053503</v>
+        <v>41.13161433526319</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>18.65108350136428</v>
+        <v>14.34201936916479</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.2202068226683432</v>
+        <v>0.5488437355316024</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.1008005308595484</v>
+        <v>0.1404900519776275</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6838</v>
+        <v>6776</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>台新藥</t>
+          <t>展碁國際</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>199.6729076614043</v>
+        <v>200.4248547505902</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>22.45</v>
+        <v>53.4</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>33.89896500287061</v>
+        <v>44.1694646053503</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>10.25999403318408</v>
+        <v>18.65108350136428</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>1.531673986514066</v>
+        <v>0.2202068226683432</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.0611221517786567</v>
+        <v>0.1008005308595484</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6573</v>
+        <v>6838</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>虹揚-KY</t>
+          <t>台新藥</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>192.1088312022304</v>
+        <v>199.6729076614043</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>16.15</v>
+        <v>22.45</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>39.6321581446012</v>
+        <v>33.89896500287061</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>14.54353156180168</v>
+        <v>10.25999403318408</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.5930023972993973</v>
+        <v>1.531673986514066</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.0731372298539557</v>
+        <v>-0.0611221517786567</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6582</v>
+        <v>6573</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>申豐</t>
+          <t>虹揚-KY</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>187.9614705236373</v>
+        <v>192.1088312022304</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>31.1</v>
+        <v>16.15</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>38.82153537863201</v>
+        <v>39.6321581446012</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>14.00987368951569</v>
+        <v>14.54353156180168</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.7503724657979695</v>
+        <v>0.5930023972993973</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,48 +6559,48 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.0395385665009954</v>
+        <v>-0.0731372298539557</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6556</v>
+        <v>6582</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>勝品</t>
+          <t>申豐</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>180.5877202802871</v>
+        <v>187.9614705236373</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>58.3</v>
+        <v>31.1</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G116" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>31.4093855171846</v>
+        <v>38.82153537863201</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>22.59030645786281</v>
+        <v>14.00987368951569</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.6311557921192702</v>
+        <v>0.7503724657979695</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.5310816185764566</v>
+        <v>-0.0395385665009954</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6725</v>
+        <v>6556</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>矽科宏晟</t>
+          <t>勝品</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>176.640695046495</v>
+        <v>180.5877202802871</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>235</v>
+        <v>58.3</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,16 +6647,16 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>33.75875661443536</v>
+        <v>31.4093855171846</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>25.32029557643385</v>
+        <v>22.59030645786281</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.3834979891108901</v>
+        <v>0.6311557921192702</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L117" s="2" t="n">
         <v>0</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.1300122479115053</v>
+        <v>-0.5310816185764566</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -6675,41 +6675,41 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6552</v>
+        <v>6725</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>易華電</t>
+          <t>矽科宏晟</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>165.2576118914638</v>
+        <v>176.640695046495</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>24.35</v>
+        <v>235</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G118" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>40.58841069995886</v>
+        <v>33.75875661443536</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>18.26968548562742</v>
+        <v>25.32029557643385</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.3394449772892452</v>
+        <v>0.3834979891108901</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L118" s="2" t="n">
         <v>0</v>
@@ -6718,48 +6718,48 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.2420139136240919</v>
+        <v>-0.1300122479115053</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6561</v>
+        <v>6552</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>是方</t>
+          <t>易華電</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>150.5054538501756</v>
+        <v>165.2576118914638</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>321.5</v>
+        <v>24.35</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G119" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>43.68806549358673</v>
+        <v>40.58841069995886</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>13.87907387696506</v>
+        <v>18.26968548562742</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.3963160978997707</v>
+        <v>0.3394449772892452</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,48 +6771,48 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.2734309273566264</v>
+        <v>0.2420139136240919</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6581</v>
+        <v>6561</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>鋼聯</t>
+          <t>是方</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>147.3706381968371</v>
+        <v>150.5054538501756</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>107.5</v>
+        <v>321.5</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G120" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>47.21742461660842</v>
+        <v>43.68806549358673</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>14.24806938160072</v>
+        <v>13.87907387696506</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>1.372340082017501</v>
+        <v>0.3963160978997707</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,48 +6824,48 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.09088435531690441</v>
+        <v>0.2734309273566264</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6732</v>
+        <v>6581</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>昇佳電子</t>
+          <t>鋼聯</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>131.6427115342403</v>
+        <v>147.3706381968371</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>155</v>
+        <v>107.5</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G121" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>40.80227789354687</v>
+        <v>47.21742461660842</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>19.6097931607593</v>
+        <v>14.24806938160072</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.4164507825579137</v>
+        <v>1.372340082017501</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,48 +6877,48 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.0200410246254785</v>
+        <v>-0.09088435531690441</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6754</v>
+        <v>6732</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>匯僑設計</t>
+          <t>昇佳電子</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>115.6172596508589</v>
+        <v>131.6427115342403</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>41.5</v>
+        <v>155</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G122" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>39.57866443830665</v>
+        <v>40.80227789354687</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>8.671643395464208</v>
+        <v>19.6097931607593</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.7803709253343134</v>
+        <v>0.4164507825579137</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.0060692667239731</v>
+        <v>-0.0200410246254785</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>6641</v>
+        <v>6754</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>基士德-KY</t>
+          <t>匯僑設計</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>115.570701165887</v>
+        <v>115.6172596508589</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>18</v>
+        <v>41.5</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>51.83556214426451</v>
+        <v>39.57866443830665</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>9.442315738035736</v>
+        <v>8.671643395464208</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.5128064873439359</v>
+        <v>0.7803709253343134</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.0549335003137702</v>
+        <v>-0.0060692667239731</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -6993,21 +6993,21 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>6614</v>
+        <v>6641</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>資拓宏宇</t>
+          <t>基士德-KY</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>114.0310118898152</v>
+        <v>115.570701165887</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>35.85</v>
+        <v>18</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>32.95378241465126</v>
+        <v>51.83556214426451</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>13.46760065026838</v>
+        <v>9.442315738035736</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.7519965578859097</v>
+        <v>0.5128064873439359</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.0537412453216027</v>
+        <v>0.0549335003137702</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7046,21 +7046,21 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>6790</v>
+        <v>6614</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>永豐實</t>
+          <t>資拓宏宇</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>113.1965062939431</v>
+        <v>114.0310118898152</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>37.9</v>
+        <v>35.85</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>35.57018027867348</v>
+        <v>32.95378241465126</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>19.35118272536087</v>
+        <v>13.46760065026838</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.646965332664773</v>
+        <v>0.7519965578859097</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.0179014628668225</v>
+        <v>0.0537412453216027</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7099,21 +7099,21 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>6794</v>
+        <v>6790</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>向榮生技-創</t>
+          <t>永豐實</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>98.107534328949</v>
+        <v>113.1965062939431</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>68.09999999999999</v>
+        <v>37.9</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>23.4138457839212</v>
+        <v>35.57018027867348</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>19.01381505964003</v>
+        <v>19.35118272536087</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>1.287372679539781</v>
+        <v>0.646965332664773</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.6582110798312311</v>
+        <v>-0.0179014628668225</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7152,52 +7152,105 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
+        <v>6794</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>向榮生技-創</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>98.107534328949</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>23.4138457839212</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>19.01381505964003</v>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>1.287372679539781</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>-0.6582110798312311</v>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
         <v>6823</v>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>濾能</t>
         </is>
       </c>
-      <c r="C127" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D127" s="2" t="n">
+      <c r="C128" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D128" s="2" t="n">
         <v>67.21719010208508</v>
       </c>
-      <c r="E127" s="2" t="n">
+      <c r="E128" s="2" t="n">
         <v>62.8</v>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="G127" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H127" s="2" t="n">
+      <c r="G128" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H128" s="2" t="n">
         <v>43.40787339230151</v>
       </c>
-      <c r="I127" s="2" t="n">
+      <c r="I128" s="2" t="n">
         <v>12.9564988644061</v>
       </c>
-      <c r="J127" s="2" t="n">
+      <c r="J128" s="2" t="n">
         <v>0.3928287632169864</v>
       </c>
-      <c r="K127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M127" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N127" s="2" t="n">
+      <c r="K128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N128" s="2" t="n">
         <v>0.0579625711931424</v>
       </c>
-      <c r="O127" s="2" t="inlineStr">
+      <c r="O128" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
